--- a/data_pur.xlsx
+++ b/data_pur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ali\belajar python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4F0DA1-3606-46EF-B0C5-CD96B2CAF82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E815E5B5-C0DE-4CC8-BDB1-2DBC4004B627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43579,7 +43579,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="705" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>704</v>
       </c>
@@ -43629,7 +43629,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="706" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>705</v>
       </c>
@@ -43682,7 +43682,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="707" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>706</v>
       </c>
@@ -43735,7 +43735,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="708" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>707</v>
       </c>
@@ -43788,7 +43788,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="709" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>708</v>
       </c>
@@ -43841,7 +43841,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="710" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>709</v>
       </c>
@@ -43894,7 +43894,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="711" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>710</v>
       </c>
@@ -43944,7 +43944,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="712" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>711</v>
       </c>
@@ -43994,7 +43994,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="713" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>712</v>
       </c>
@@ -44047,7 +44047,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="714" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>713</v>
       </c>
@@ -44100,7 +44100,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="715" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>714</v>
       </c>
@@ -44150,7 +44150,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="716" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>715</v>
       </c>
@@ -44200,7 +44200,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="717" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>716</v>
       </c>
@@ -44250,7 +44250,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="718" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>717</v>
       </c>
@@ -44300,7 +44300,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="719" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>718</v>
       </c>
@@ -44350,7 +44350,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="720" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>719</v>
       </c>
@@ -44360,8 +44360,8 @@
       <c r="C720" s="1">
         <v>46106</v>
       </c>
-      <c r="D720" t="s">
-        <v>20</v>
+      <c r="D720" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F720" t="s">
         <v>1719</v>
@@ -44395,6 +44395,9 @@
       </c>
       <c r="R720" s="1">
         <v>46106</v>
+      </c>
+      <c r="S720" s="1">
+        <v>46108</v>
       </c>
     </row>
     <row r="721" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">

--- a/data_pur.xlsx
+++ b/data_pur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ali\belajar python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E815E5B5-C0DE-4CC8-BDB1-2DBC4004B627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A937F76-9F86-4DF1-923C-1BC901D0397C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44210,8 +44210,8 @@
       <c r="C717" s="1">
         <v>46106</v>
       </c>
-      <c r="D717" t="s">
-        <v>20</v>
+      <c r="D717" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F717" t="s">
         <v>1058</v>
@@ -44248,6 +44248,9 @@
       </c>
       <c r="R717" s="1">
         <v>46106</v>
+      </c>
+      <c r="S717" s="1">
+        <v>46109</v>
       </c>
     </row>
     <row r="718" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -44260,8 +44263,8 @@
       <c r="C718" s="1">
         <v>46106</v>
       </c>
-      <c r="D718" t="s">
-        <v>20</v>
+      <c r="D718" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F718" t="s">
         <v>1052</v>
@@ -44298,6 +44301,9 @@
       </c>
       <c r="R718" s="1">
         <v>46106</v>
+      </c>
+      <c r="S718" s="1">
+        <v>46109</v>
       </c>
     </row>
     <row r="719" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
@@ -44310,8 +44316,8 @@
       <c r="C719" s="1">
         <v>46106</v>
       </c>
-      <c r="D719" t="s">
-        <v>20</v>
+      <c r="D719" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F719" t="s">
         <v>1057</v>
@@ -44348,6 +44354,9 @@
       </c>
       <c r="R719" s="1">
         <v>46106</v>
+      </c>
+      <c r="S719" s="1">
+        <v>46109</v>
       </c>
     </row>
     <row r="720" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">

--- a/data_pur.xlsx
+++ b/data_pur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ali\belajar python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A937F76-9F86-4DF1-923C-1BC901D0397C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DC3329-6C71-4B5F-A723-6C5081DA2BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
